--- a/datos/repositorio_jerarquia_supervisores.xlsx
+++ b/datos/repositorio_jerarquia_supervisores.xlsx
@@ -72,7 +72,7 @@
       </c>
       <c r="B1" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">SUPERVISOR REAL</t>
+          <t xml:space="preserve">JEFE DE AGENCIA</t>
         </is>
       </c>
     </row>
